--- a/docs/School-Management-QA-Audit.xlsx
+++ b/docs/School-Management-QA-Audit.xlsx
@@ -1,14 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="23040" windowHeight="9000" activeTab="1"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Summary" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Bugs" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Role-Service Matrix" state="visible" r:id="rId6"/>
+    <sheet name="Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="Bugs" sheetId="2" r:id="rId2"/>
+    <sheet name="Role-Service Matrix" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Bugs!$A$1:$H$27</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1407,42 +1426,218 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="27">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <family val="2"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FFB91C1C"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="10"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <color rgb="FFB91C1C"/>
-      <sz val="10"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1452,40 +1647,233 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F2937"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFECACA"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDCFCE7"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFED7AA"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFEF9C3"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE0E7FF"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFEE2E2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1493,30 +1881,262 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1537,21 +2157,75 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1873,123 +2547,123 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor rgb="FF2563EB"/>
   </sheetPr>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="42" style="1" customWidth="1"/>
-    <col min="2" max="2" width="90" style="2" customWidth="1"/>
+    <col min="1" max="1" width="42" style="2" customWidth="1"/>
+    <col min="2" max="2" width="90" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="13" customFormat="1" ht="21" spans="1:2">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:2">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+    <row r="4" s="14" customFormat="1" ht="28.8" spans="1:2">
+      <c r="A4" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:2">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:2">
+      <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:2">
+      <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="10" s="2" customFormat="1" spans="1:2">
+      <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+    <row r="11" ht="28.8" spans="1:2">
+      <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+    <row r="12" ht="28.8" spans="1:2">
+      <c r="A12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+    <row r="14" s="2" customFormat="1" spans="1:2">
+      <c r="A14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+    <row r="15" s="14" customFormat="1" ht="43.2" spans="1:2">
+      <c r="A15" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr filterMode="1">
     <tabColor rgb="FFDC2626"/>
   </sheetPr>
   <dimension ref="A1:H27"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -2000,721 +2674,735 @@
     <col min="8" max="8" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row r="1" ht="22" customHeight="1" spans="1:8">
+      <c r="A1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+    <row r="2" s="1" customFormat="1" ht="57.6" hidden="1" spans="1:8">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+    <row r="3" s="1" customFormat="1" ht="57.6" hidden="1" spans="1:8">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+    <row r="4" s="1" customFormat="1" ht="72" hidden="1" spans="1:8">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+    <row r="5" s="1" customFormat="1" ht="57.6" hidden="1" spans="1:8">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+    <row r="6" s="1" customFormat="1" ht="115.2" hidden="1" spans="1:8">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+    <row r="7" s="1" customFormat="1" ht="43.2" hidden="1" spans="1:8">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+    <row r="8" s="1" customFormat="1" ht="57.6" hidden="1" spans="1:8">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+    <row r="9" s="1" customFormat="1" ht="57.6" hidden="1" spans="1:8">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+    <row r="10" s="1" customFormat="1" ht="72" hidden="1" spans="1:8">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+    <row r="11" s="1" customFormat="1" ht="72" hidden="1" spans="1:8">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+    <row r="12" s="1" customFormat="1" ht="72" hidden="1" spans="1:8">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+    <row r="13" s="1" customFormat="1" ht="43.2" hidden="1" spans="1:8">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+    <row r="14" s="1" customFormat="1" ht="115.2" hidden="1" spans="1:8">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+    <row r="15" s="1" customFormat="1" ht="57.6" hidden="1" spans="1:8">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+    <row r="16" s="1" customFormat="1" ht="72" spans="1:8">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="17" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+    <row r="17" s="1" customFormat="1" ht="57.6" spans="1:8">
+      <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="G17" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="18" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+    <row r="18" s="1" customFormat="1" ht="86.4" spans="1:8">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+    <row r="19" s="1" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G19" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+    <row r="20" s="1" customFormat="1" ht="115.2" spans="1:8">
+      <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G20" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="21" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+    <row r="21" s="1" customFormat="1" ht="57.6" spans="1:8">
+      <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="22" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+    <row r="22" s="1" customFormat="1" ht="129.6" spans="1:8">
+      <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="H22" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="23" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+    <row r="23" s="1" customFormat="1" ht="115.2" spans="1:8">
+      <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="G23" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="H23" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+    <row r="24" s="1" customFormat="1" ht="86.4" spans="1:8">
+      <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="G24" s="14" t="s">
+      <c r="G24" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H24" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="25" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+    <row r="25" s="1" customFormat="1" ht="43.2" hidden="1" spans="1:8">
+      <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="G25" s="10" t="s">
+      <c r="G25" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="26" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+    <row r="26" s="1" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="G26" s="14" t="s">
+      <c r="G26" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H26" s="1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="27" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+    <row r="27" s="1" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G27" s="14" t="s">
+      <c r="G27" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="H27" s="1" t="s">
         <v>160</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H27" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="Unfixed (by design for demo)"/>
+        <filter val="Unfixed (appears intentional)"/>
+        <filter val="Unfixed (informational)"/>
+        <filter val="Unfixed (logged — low risk)"/>
+        <filter val="Unfixed (informational — architecture as designed)"/>
+        <filter val="Unfixed (logged)"/>
+      </filters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor rgb="FF16A34A"/>
   </sheetPr>
   <dimension ref="A1:E156"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
@@ -2722,2590 +3410,2586 @@
     <col min="5" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+    <row r="1" ht="18" spans="1:5">
+      <c r="A1" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-    </row>
-    <row r="4" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" ht="22" customHeight="1"/>
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A5" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row r="6" s="1" customFormat="1" spans="1:5">
+      <c r="A6" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="7" s="1" customFormat="1" spans="1:5">
+      <c r="A7" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row r="8" s="1" customFormat="1" spans="1:5">
+      <c r="A8" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row r="9" s="1" customFormat="1" spans="1:5">
+      <c r="A9" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    <row r="10" s="1" customFormat="1" spans="1:5">
+      <c r="A10" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A11" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="12" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A12" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="1" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    <row r="13" s="1" customFormat="1" spans="1:5">
+      <c r="A13" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="14" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A14" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="15" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A15" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="16" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A16" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="1" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="17" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+    <row r="17" s="1" customFormat="1" spans="1:5">
+      <c r="A17" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="1" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="18" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+    <row r="18" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A18" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+    <row r="19" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A19" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="20" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+    <row r="20" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A20" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="1" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+    <row r="21" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A21" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+    <row r="22" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A22" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="23" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+    <row r="23" s="1" customFormat="1" spans="1:5">
+      <c r="A23" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="24" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+    <row r="24" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A24" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="25" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+    <row r="25" s="1" customFormat="1" spans="1:5">
+      <c r="A25" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="1" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="26" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+    <row r="26" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A26" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="1" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+    <row r="27" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A27" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="28" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+    <row r="28" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A28" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="1" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+    <row r="29" s="1" customFormat="1" spans="1:5">
+      <c r="A29" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="1" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="30" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+    <row r="30" s="1" customFormat="1" spans="1:5">
+      <c r="A30" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="1" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="31" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+    <row r="31" s="1" customFormat="1" spans="1:5">
+      <c r="A31" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="1" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="32" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
+    <row r="32" s="1" customFormat="1" spans="1:5">
+      <c r="A32" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="1" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="33" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+    <row r="33" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A33" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="1" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="34" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+    <row r="34" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A34" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="1" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="35" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
+    <row r="35" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A35" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="1" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="36" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+    <row r="36" s="1" customFormat="1" spans="1:5">
+      <c r="A36" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="1" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="37" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
+    <row r="37" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A37" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="1" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="38" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
+    <row r="38" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A38" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" s="1" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="39" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
+    <row r="39" s="1" customFormat="1" spans="1:5">
+      <c r="A39" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="1" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="40" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
+    <row r="40" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A40" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" s="1" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="41" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
+    <row r="41" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A41" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="42" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
+    <row r="42" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A42" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="43" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
+    <row r="43" s="1" customFormat="1" spans="1:5">
+      <c r="A43" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" s="1" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="44" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
+    <row r="44" s="1" customFormat="1" spans="1:5">
+      <c r="A44" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D44" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="45" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
+    <row r="45" s="1" customFormat="1" spans="1:5">
+      <c r="A45" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="46" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
+    <row r="46" s="1" customFormat="1" spans="1:5">
+      <c r="A46" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E46" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="47" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
+    <row r="47" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A47" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E47" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="48" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
+    <row r="48" s="1" customFormat="1" spans="1:5">
+      <c r="A48" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E48" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="49" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
+    <row r="49" s="1" customFormat="1" spans="1:5">
+      <c r="A49" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="E49" s="1" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="50" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
+    <row r="50" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A50" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E50" s="1" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="51" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
+    <row r="51" s="1" customFormat="1" spans="1:5">
+      <c r="A51" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="E51" s="1" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="52" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
+    <row r="52" s="1" customFormat="1" spans="1:5">
+      <c r="A52" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E52" s="1" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="53" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
+    <row r="53" s="1" customFormat="1" spans="1:5">
+      <c r="A53" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="E53" s="1" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="54" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
+    <row r="54" s="1" customFormat="1" spans="1:5">
+      <c r="A54" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D54" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="E54" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="55" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
+    <row r="55" s="1" customFormat="1" spans="1:5">
+      <c r="A55" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="E55" s="1" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="56" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
+    <row r="56" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A56" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D56" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E56" s="1" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="57" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
+    <row r="57" s="1" customFormat="1" spans="1:5">
+      <c r="A57" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D57" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E57" s="1" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="58" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
+    <row r="58" s="1" customFormat="1" spans="1:5">
+      <c r="A58" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D58" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="E58" s="1" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="59" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
+    <row r="59" s="1" customFormat="1" spans="1:5">
+      <c r="A59" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D59" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="E59" s="1" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="60" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
+    <row r="60" s="1" customFormat="1" spans="1:5">
+      <c r="A60" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D60" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="E60" s="1" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="61" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
+    <row r="61" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A61" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D61" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="E61" s="1" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="62" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
+    <row r="62" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A62" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D62" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="E62" s="1" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="63" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
+    <row r="63" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A63" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="D63" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="E63" s="1" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="64" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
+    <row r="64" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A64" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D64" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E64" s="2" t="s">
+      <c r="E64" s="1" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="65" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="2" t="s">
+    <row r="65" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A65" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="D65" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="E65" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="66" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
+    <row r="66" s="1" customFormat="1" spans="1:5">
+      <c r="A66" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="D66" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E66" s="2" t="s">
+      <c r="E66" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="67" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
+    <row r="67" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A67" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="D67" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E67" s="2" t="s">
+      <c r="E67" s="1" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="68" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
+    <row r="68" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A68" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="D68" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E68" s="2" t="s">
+      <c r="E68" s="1" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="69" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
+    <row r="69" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A69" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="D69" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E69" s="2" t="s">
+      <c r="E69" s="1" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="70" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
+    <row r="70" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A70" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="D70" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E70" s="2" t="s">
+      <c r="E70" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="71" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="2" t="s">
+    <row r="71" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A71" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="D71" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E71" s="2" t="s">
+      <c r="E71" s="1" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="72" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
+    <row r="72" s="1" customFormat="1" spans="1:5">
+      <c r="A72" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="D72" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E72" s="2" t="s">
+      <c r="E72" s="1" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="73" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="2" t="s">
+    <row r="73" s="1" customFormat="1" spans="1:5">
+      <c r="A73" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="D73" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E73" s="2" t="s">
+      <c r="E73" s="1" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="74" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
+    <row r="74" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A74" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="D74" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E74" s="2" t="s">
+      <c r="E74" s="1" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="75" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
+    <row r="75" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A75" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="D75" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E75" s="2" t="s">
+      <c r="E75" s="1" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="76" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
+    <row r="76" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A76" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="D76" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E76" s="2" t="s">
+      <c r="E76" s="1" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="77" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="2" t="s">
+    <row r="77" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A77" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="D77" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E77" s="2" t="s">
+      <c r="E77" s="1" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="78" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="2" t="s">
+    <row r="78" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A78" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="D78" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E78" s="2" t="s">
+      <c r="E78" s="1" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="79" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="2" t="s">
+    <row r="79" s="1" customFormat="1" spans="1:5">
+      <c r="A79" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B79" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="D79" s="2" t="s">
+      <c r="D79" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E79" s="2" t="s">
+      <c r="E79" s="1" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="80" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="2" t="s">
+    <row r="80" s="1" customFormat="1" spans="1:5">
+      <c r="A80" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="D80" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E80" s="2" t="s">
+      <c r="E80" s="1" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="81" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="2" t="s">
+    <row r="81" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A81" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B81" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="D81" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E81" s="2" t="s">
+      <c r="E81" s="1" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="82" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="2" t="s">
+    <row r="82" s="1" customFormat="1" spans="1:5">
+      <c r="A82" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B82" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="D82" s="2" t="s">
+      <c r="D82" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E82" s="2" t="s">
+      <c r="E82" s="1" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="83" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="2" t="s">
+    <row r="83" s="1" customFormat="1" spans="1:5">
+      <c r="A83" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B83" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C83" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="D83" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E83" s="2" t="s">
+      <c r="E83" s="1" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="84" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="2" t="s">
+    <row r="84" s="1" customFormat="1" spans="1:5">
+      <c r="A84" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B84" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C84" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="D84" s="2" t="s">
+      <c r="D84" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E84" s="2" t="s">
+      <c r="E84" s="1" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="85" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="2" t="s">
+    <row r="85" s="1" customFormat="1" spans="1:5">
+      <c r="A85" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B85" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="D85" s="2" t="s">
+      <c r="D85" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E85" s="2" t="s">
+      <c r="E85" s="1" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="86" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="2" t="s">
+    <row r="86" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A86" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="B86" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C86" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="D86" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E86" s="2" t="s">
+      <c r="E86" s="1" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="87" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="2" t="s">
+    <row r="87" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A87" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="B87" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="D87" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E87" s="2" t="s">
+      <c r="E87" s="1" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="88" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
+    <row r="88" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A88" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="B88" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C88" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="D88" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E88" s="2" t="s">
+      <c r="E88" s="1" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="89" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="2" t="s">
+    <row r="89" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A89" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="B89" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="D89" s="2" t="s">
+      <c r="D89" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E89" s="2" t="s">
+      <c r="E89" s="1" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="90" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
+    <row r="90" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A90" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B90" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C90" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="D90" s="2" t="s">
+      <c r="D90" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E90" s="2" t="s">
+      <c r="E90" s="1" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="91" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="2" t="s">
+    <row r="91" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A91" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B91" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C91" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="D91" s="2" t="s">
+      <c r="D91" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E91" s="2" t="s">
+      <c r="E91" s="1" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="92" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="2" t="s">
+    <row r="92" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A92" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B92" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="D92" s="2" t="s">
+      <c r="D92" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E92" s="2" t="s">
+      <c r="E92" s="1" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="93" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="2" t="s">
+    <row r="93" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A93" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B93" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C93" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="D93" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E93" s="2" t="s">
+      <c r="E93" s="1" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="94" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="2" t="s">
+    <row r="94" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A94" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="B94" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C94" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="D94" s="2" t="s">
+      <c r="D94" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E94" s="2" t="s">
+      <c r="E94" s="1" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="95" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="2" t="s">
+    <row r="95" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A95" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="B95" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C95" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="D95" s="2" t="s">
+      <c r="D95" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E95" s="2" t="s">
+      <c r="E95" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="96" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="2" t="s">
+    <row r="96" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A96" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="B96" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C96" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="D96" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E96" s="2" t="s">
+      <c r="E96" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="97" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="2" t="s">
+    <row r="97" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A97" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="B97" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C97" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="D97" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E97" s="2" t="s">
+      <c r="E97" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="98" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="2" t="s">
+    <row r="98" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A98" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="B98" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C98" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="D98" s="2" t="s">
+      <c r="D98" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E98" s="2" t="s">
+      <c r="E98" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="99" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="2" t="s">
+    <row r="99" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A99" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="B99" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C99" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="D99" s="2" t="s">
+      <c r="D99" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E99" s="2" t="s">
+      <c r="E99" s="1" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="100" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="2" t="s">
+    <row r="100" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A100" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B100" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C100" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="D100" s="2" t="s">
+      <c r="D100" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E100" s="2" t="s">
+      <c r="E100" s="1" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="101" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="2" t="s">
+    <row r="101" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A101" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="B101" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="C101" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="D101" s="2" t="s">
+      <c r="D101" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E101" s="2" t="s">
+      <c r="E101" s="1" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="102" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="2" t="s">
+    <row r="102" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A102" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="B102" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C102" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="D102" s="2" t="s">
+      <c r="D102" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E102" s="2" t="s">
+      <c r="E102" s="1" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="103" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="2" t="s">
+    <row r="103" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A103" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B103" s="2" t="s">
+      <c r="B103" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="C103" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="D103" s="2" t="s">
+      <c r="D103" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E103" s="2" t="s">
+      <c r="E103" s="1" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="104" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="2" t="s">
+    <row r="104" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A104" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="B104" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C104" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="D104" s="2" t="s">
+      <c r="D104" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E104" s="2" t="s">
+      <c r="E104" s="1" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="105" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="2" t="s">
+    <row r="105" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A105" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="B105" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="C105" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="D105" s="2" t="s">
+      <c r="D105" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E105" s="2" t="s">
+      <c r="E105" s="1" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="106" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="2" t="s">
+    <row r="106" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A106" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="B106" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C106" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="D106" s="2" t="s">
+      <c r="D106" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E106" s="2" t="s">
+      <c r="E106" s="1" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="107" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="2" t="s">
+    <row r="107" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A107" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="B107" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="C107" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="D107" s="2" t="s">
+      <c r="D107" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E107" s="2" t="s">
+      <c r="E107" s="1" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="108" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="2" t="s">
+    <row r="108" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A108" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="B108" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="C108" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="D108" s="2" t="s">
+      <c r="D108" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E108" s="2" t="s">
+      <c r="E108" s="1" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="109" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="2" t="s">
+    <row r="109" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A109" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="B109" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C109" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="D109" s="2" t="s">
+      <c r="D109" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E109" s="2" t="s">
+      <c r="E109" s="1" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="110" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="2" t="s">
+    <row r="110" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A110" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="B110" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C110" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="D110" s="2" t="s">
+      <c r="D110" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E110" s="2" t="s">
+      <c r="E110" s="1" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="111" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="2" t="s">
+    <row r="111" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A111" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="B111" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="C111" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="D111" s="2" t="s">
+      <c r="D111" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E111" s="2" t="s">
+      <c r="E111" s="1" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="112" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="2" t="s">
+    <row r="112" s="1" customFormat="1" spans="1:5">
+      <c r="A112" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="B112" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C112" s="2" t="s">
+      <c r="C112" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="D112" s="2" t="s">
+      <c r="D112" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="E112" s="2" t="s">
+      <c r="E112" s="1" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="113" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="2" t="s">
+    <row r="113" s="1" customFormat="1" spans="1:5">
+      <c r="A113" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="B113" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="C113" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D113" s="2" t="s">
+      <c r="D113" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E113" s="2" t="s">
+      <c r="E113" s="1" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="114" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="2" t="s">
+    <row r="114" s="1" customFormat="1" spans="1:5">
+      <c r="A114" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="B114" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C114" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="D114" s="2" t="s">
+      <c r="D114" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="E114" s="2" t="s">
+      <c r="E114" s="1" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="115" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="2" t="s">
+    <row r="115" s="1" customFormat="1" spans="1:5">
+      <c r="A115" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="B115" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="C115" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="D115" s="2" t="s">
+      <c r="D115" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E115" s="2" t="s">
+      <c r="E115" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="116" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="2" t="s">
+    <row r="116" s="1" customFormat="1" spans="1:5">
+      <c r="A116" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="B116" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="C116" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="D116" s="2" t="s">
+      <c r="D116" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E116" s="2" t="s">
+      <c r="E116" s="1" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="117" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="2" t="s">
+    <row r="117" s="1" customFormat="1" spans="1:5">
+      <c r="A117" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="B117" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="C117" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="D117" s="2" t="s">
+      <c r="D117" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="E117" s="2" t="s">
+      <c r="E117" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="118" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="2" t="s">
+    <row r="118" s="1" customFormat="1" spans="1:5">
+      <c r="A118" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="B118" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C118" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="D118" s="2" t="s">
+      <c r="D118" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="E118" s="2" t="s">
+      <c r="E118" s="1" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="119" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="2" t="s">
+    <row r="119" s="1" customFormat="1" spans="1:5">
+      <c r="A119" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="B119" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C119" s="2" t="s">
+      <c r="C119" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="D119" s="2" t="s">
+      <c r="D119" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="E119" s="2" t="s">
+      <c r="E119" s="1" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="120" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="2" t="s">
+    <row r="120" s="1" customFormat="1" spans="1:5">
+      <c r="A120" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="B120" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C120" s="2" t="s">
+      <c r="C120" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="D120" s="2" t="s">
+      <c r="D120" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="E120" s="2" t="s">
+      <c r="E120" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="121" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="2" t="s">
+    <row r="121" s="1" customFormat="1" spans="1:5">
+      <c r="A121" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="B121" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C121" s="2" t="s">
+      <c r="C121" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="D121" s="2" t="s">
+      <c r="D121" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="E121" s="2" t="s">
+      <c r="E121" s="1" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="122" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="2" t="s">
+    <row r="122" s="1" customFormat="1" spans="1:5">
+      <c r="A122" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="B122" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="C122" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="D122" s="2" t="s">
+      <c r="D122" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="E122" s="2" t="s">
+      <c r="E122" s="1" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="123" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="2" t="s">
+    <row r="123" s="1" customFormat="1" spans="1:5">
+      <c r="A123" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="B123" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C123" s="2" t="s">
+      <c r="C123" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="D123" s="2" t="s">
+      <c r="D123" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="E123" s="2" t="s">
+      <c r="E123" s="1" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="124" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="2" t="s">
+    <row r="124" s="1" customFormat="1" spans="1:5">
+      <c r="A124" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="B124" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="C124" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="D124" s="2" t="s">
+      <c r="D124" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E124" s="2" t="s">
+      <c r="E124" s="1" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="125" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="2" t="s">
+    <row r="125" s="1" customFormat="1" spans="1:5">
+      <c r="A125" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="B125" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="C125" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="D125" s="2" t="s">
+      <c r="D125" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E125" s="2" t="s">
+      <c r="E125" s="1" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="126" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="2" t="s">
+    <row r="126" s="1" customFormat="1" spans="1:5">
+      <c r="A126" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="B126" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C126" s="2" t="s">
+      <c r="C126" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="D126" s="2" t="s">
+      <c r="D126" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E126" s="2" t="s">
+      <c r="E126" s="1" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="127" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="2" t="s">
+    <row r="127" s="1" customFormat="1" spans="1:5">
+      <c r="A127" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="B127" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C127" s="2" t="s">
+      <c r="C127" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="D127" s="2" t="s">
+      <c r="D127" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="E127" s="2" t="s">
+      <c r="E127" s="1" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="128" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="2" t="s">
+    <row r="128" s="1" customFormat="1" spans="1:5">
+      <c r="A128" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="B128" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C128" s="2" t="s">
+      <c r="C128" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D128" s="2" t="s">
+      <c r="D128" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="E128" s="2" t="s">
+      <c r="E128" s="1" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="129" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="2" t="s">
+    <row r="129" s="1" customFormat="1" spans="1:5">
+      <c r="A129" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="B129" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C129" s="2" t="s">
+      <c r="C129" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="D129" s="2" t="s">
+      <c r="D129" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="E129" s="2" t="s">
+      <c r="E129" s="1" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="130" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="2" t="s">
+    <row r="130" s="1" customFormat="1" spans="1:5">
+      <c r="A130" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="B130" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C130" s="2" t="s">
+      <c r="C130" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D130" s="2" t="s">
+      <c r="D130" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="E130" s="2" t="s">
+      <c r="E130" s="1" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="131" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="2" t="s">
+    <row r="131" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A131" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="B131" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="C131" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D131" s="2" t="s">
+      <c r="D131" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="E131" s="2" t="s">
+      <c r="E131" s="1" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="132" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="2" t="s">
+    <row r="132" s="1" customFormat="1" spans="1:5">
+      <c r="A132" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="B132" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="C132" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="D132" s="2" t="s">
+      <c r="D132" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="E132" s="2" t="s">
+      <c r="E132" s="1" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="133" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="2" t="s">
+    <row r="133" s="1" customFormat="1" spans="1:5">
+      <c r="A133" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="B133" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C133" s="2" t="s">
+      <c r="C133" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="D133" s="2" t="s">
+      <c r="D133" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="E133" s="2" t="s">
+      <c r="E133" s="1" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="134" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="2" t="s">
+    <row r="134" s="1" customFormat="1" spans="1:5">
+      <c r="A134" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="B134" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="C134" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="D134" s="2" t="s">
+      <c r="D134" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="E134" s="2" t="s">
+      <c r="E134" s="1" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="135" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="2" t="s">
+    <row r="135" s="1" customFormat="1" spans="1:5">
+      <c r="A135" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="B135" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C135" s="2" t="s">
+      <c r="C135" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="D135" s="2" t="s">
+      <c r="D135" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="E135" s="2" t="s">
+      <c r="E135" s="1" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="136" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="2" t="s">
+    <row r="136" s="1" customFormat="1" spans="1:5">
+      <c r="A136" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="B136" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C136" s="2" t="s">
+      <c r="C136" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="D136" s="2" t="s">
+      <c r="D136" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="E136" s="2" t="s">
+      <c r="E136" s="1" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="137" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="2" t="s">
+    <row r="137" s="1" customFormat="1" spans="1:5">
+      <c r="A137" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="B137" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C137" s="2" t="s">
+      <c r="C137" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="D137" s="2" t="s">
+      <c r="D137" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="E137" s="2" t="s">
+      <c r="E137" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="138" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="2" t="s">
+    <row r="138" s="1" customFormat="1" spans="1:5">
+      <c r="A138" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="B138" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C138" s="2" t="s">
+      <c r="C138" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="D138" s="2" t="s">
+      <c r="D138" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="E138" s="2" t="s">
+      <c r="E138" s="1" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="139" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="2" t="s">
+    <row r="139" s="1" customFormat="1" spans="1:5">
+      <c r="A139" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="B139" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C139" s="2" t="s">
+      <c r="C139" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="D139" s="2" t="s">
+      <c r="D139" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="E139" s="2" t="s">
+      <c r="E139" s="1" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="140" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="2" t="s">
+    <row r="140" s="1" customFormat="1" spans="1:5">
+      <c r="A140" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="B140" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="C140" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="D140" s="2" t="s">
+      <c r="D140" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="E140" s="2" t="s">
+      <c r="E140" s="1" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="141" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="2" t="s">
+    <row r="141" s="1" customFormat="1" spans="1:5">
+      <c r="A141" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="B141" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C141" s="2" t="s">
+      <c r="C141" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="D141" s="2" t="s">
+      <c r="D141" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E141" s="2" t="s">
+      <c r="E141" s="1" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="143" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="1" t="s">
+    <row r="143" s="2" customFormat="1" spans="1:5">
+      <c r="A143" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="B143" s="1"/>
-      <c r="C143" s="1"/>
-      <c r="D143" s="1"/>
-      <c r="E143" s="1"/>
-    </row>
-    <row r="144" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="2" t="s">
+    </row>
+    <row r="144" s="1" customFormat="1" spans="1:5">
+      <c r="A144" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B144" s="2" t="s">
+      <c r="B144" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C144" s="2" t="s">
+      <c r="C144" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="D144" s="2" t="s">
+      <c r="D144" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="E144" s="2" t="s">
+      <c r="E144" s="1" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="145" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="2" t="s">
+    <row r="145" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A145" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B145" s="2" t="s">
+      <c r="B145" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="C145" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="D145" s="2" t="s">
+      <c r="D145" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="E145" s="2" t="s">
+      <c r="E145" s="1" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="146" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="2" t="s">
+    <row r="146" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A146" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B146" s="2" t="s">
+      <c r="B146" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C146" s="2" t="s">
+      <c r="C146" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="D146" s="2" t="s">
+      <c r="D146" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="E146" s="2" t="s">
+      <c r="E146" s="1" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="147" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="2" t="s">
+    <row r="147" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A147" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B147" s="2" t="s">
+      <c r="B147" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C147" s="2" t="s">
+      <c r="C147" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="D147" s="2" t="s">
+      <c r="D147" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="E147" s="2" t="s">
+      <c r="E147" s="1" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="148" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="2" t="s">
+    <row r="148" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A148" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B148" s="2" t="s">
+      <c r="B148" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C148" s="2" t="s">
+      <c r="C148" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D148" s="2" t="s">
+      <c r="D148" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="E148" s="2" t="s">
+      <c r="E148" s="1" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="149" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="2" t="s">
+    <row r="149" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A149" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B149" s="2" t="s">
+      <c r="B149" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C149" s="2" t="s">
+      <c r="C149" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="D149" s="2" t="s">
+      <c r="D149" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="E149" s="2" t="s">
+      <c r="E149" s="1" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="150" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="2" t="s">
+    <row r="150" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A150" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B150" s="2" t="s">
+      <c r="B150" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C150" s="2" t="s">
+      <c r="C150" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="D150" s="2" t="s">
+      <c r="D150" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="E150" s="2" t="s">
+      <c r="E150" s="1" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="151" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="2" t="s">
+    <row r="151" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A151" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="B151" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="C151" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="D151" s="2" t="s">
+      <c r="D151" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="E151" s="2" t="s">
+      <c r="E151" s="1" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="152" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="2" t="s">
+    <row r="152" s="1" customFormat="1" ht="28.8" spans="1:5">
+      <c r="A152" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B152" s="2" t="s">
+      <c r="B152" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C152" s="2" t="s">
+      <c r="C152" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="D152" s="2" t="s">
+      <c r="D152" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="E152" s="2" t="s">
+      <c r="E152" s="1" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="153" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="2" t="s">
+    <row r="153" s="1" customFormat="1" spans="1:5">
+      <c r="A153" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B153" s="2" t="s">
+      <c r="B153" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C153" s="2" t="s">
+      <c r="C153" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="D153" s="2" t="s">
+      <c r="D153" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="E153" s="2" t="s">
+      <c r="E153" s="1" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="154" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="2" t="s">
+    <row r="154" s="1" customFormat="1" spans="1:5">
+      <c r="A154" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="B154" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C154" s="2" t="s">
+      <c r="C154" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="D154" s="2" t="s">
+      <c r="D154" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="E154" s="2" t="s">
+      <c r="E154" s="1" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="155" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="2" t="s">
+    <row r="155" s="1" customFormat="1" spans="1:5">
+      <c r="A155" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B155" s="2" t="s">
+      <c r="B155" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C155" s="2" t="s">
+      <c r="C155" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D155" s="2" t="s">
+      <c r="D155" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="E155" s="2" t="s">
+      <c r="E155" s="1" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="156" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="2" t="s">
+    <row r="156" s="1" customFormat="1" spans="1:5">
+      <c r="A156" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B156" s="2" t="s">
+      <c r="B156" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C156" s="2" t="s">
+      <c r="C156" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="D156" s="2" t="s">
+      <c r="D156" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="E156" s="2" t="s">
+      <c r="E156" s="1" t="s">
         <v>462</v>
       </c>
     </row>
@@ -5317,6 +6001,7 @@
     <mergeCell ref="A143:E143"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>